--- a/import-templates/import-template-sites.xlsx
+++ b/import-templates/import-template-sites.xlsx
@@ -50,7 +50,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -72,6 +72,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F4F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -103,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,6 +133,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -146,7 +155,7 @@
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1" style="3"/>
     <col min="8" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -156,7 +165,7 @@
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">customer_code</t>
         </is>
@@ -218,7 +227,7 @@
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">customer_code</t>
         </is>
@@ -405,7 +414,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">หัวคอลัมน์สีส้ม = จำเป็นต้องกรอก / สีเขียว = ไม่บังคับ (เว้นว่างได้)</t>
+          <t xml:space="preserve">หัวคอลัมน์สีส้ม = จำเป็นต้องกรอก / สีเหลือง = ไม่บังคับ แต่แนะนำอย่างยิ่ง / สีเขียว = เว้นว่างได้</t>
         </is>
       </c>
     </row>
@@ -491,7 +500,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">แนะนำ</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -501,7 +510,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">รหัสลูกค้า (ตรงกับ companies.customer_code ที่ย้ายมาจาก Venio) — วิธีจับคู่บริษัทที่แม่นที่สุด</t>
+          <t xml:space="preserve">รหัสลูกค้า (ตรงกับ customer_code ในเทมเพลตลูกค้า) — วิธีจับคู่บริษัทที่แม่นที่สุด</t>
         </is>
       </c>
     </row>

--- a/import-templates/import-template-sites.xlsx
+++ b/import-templates/import-template-sites.xlsx
@@ -146,17 +146,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1" style="3"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1" style="3"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -167,58 +168,64 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">tax_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">customer_code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">company_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">address</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">map_url</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">contact_name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">contact_phone</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -229,35 +236,40 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">tax_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">customer_code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">company_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">address</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">map_url</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">contact_name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">contact_phone</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -266,40 +278,45 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงงานบางปู เฟส 2</t>
+          <t xml:space="preserve">PT บางปู สมุทรปราการ</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00142</t>
+          <t xml:space="preserve">0105536000123</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง จำกัด</t>
+          <t xml:space="preserve">GS20260012</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง ปิโตรเลียม จำกัด</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">88/9 ม.4 ถ.สุขุมวิท ต.บางปูใหม่ อ.เมือง จ.สมุทรปราการ 10280</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">https://maps.app.goo.gl/xxxxxxxx</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">สมชาย ใจดี</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">081-234-5678</t>
-        </is>
-      </c>
       <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0812345678</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">เข้าพื้นที่ได้ จ-ศ 08:00-17:00 ต้องแจ้ง รปภ. ล่วงหน้า 1 วัน</t>
         </is>
@@ -313,55 +330,61 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00187</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">บริษัท เอ็นเนอร์ยี่ พลัส จำกัด</t>
-        </is>
-      </c>
+          <t xml:space="preserve">0105551000456</t>
+        </is>
+      </c>
+      <c r="C3" s="9"/>
       <c r="D3" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">ห้างหุ้นส่วนจำกัด เอ็นเนอร์ยี่ พลัส</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">159 ซ.ฉลองกรุง 31 แขวงลำปลาทิว เขตลาดกระบัง กรุงเทพฯ 10520</t>
         </is>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">วราภรณ์ ศรีสุข</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">089-876-5432</t>
         </is>
       </c>
-      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">จับคู่บริษัทด้วย tax_id</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">สาขาระยอง (หลังคาอาคาร A)</t>
+          <t xml:space="preserve">สาขาระยอง (อาคาร A)</t>
         </is>
       </c>
       <c r="B4" s="9"/>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง จำกัด</t>
-        </is>
-      </c>
+      <c r="C4" s="9"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 ถ.สุขุมวิท ต.เนินพระ อ.เมืองระยอง จ.ระยอง 21000</t>
-        </is>
-      </c>
-      <c r="E4" s="9"/>
+          <t xml:space="preserve">บริษัท สุขสบาย เซอร์วิส จำกัด</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">พิกัด 12.681940, 101.276360</t>
+        </is>
+      </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">หลังคาสูง ต้องใช้ชุดกันตก</t>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">มีแต่พิกัด ไม่มีที่อยู่เต็ม</t>
         </is>
       </c>
     </row>
@@ -379,7 +402,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -428,79 +451,59 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">บริษัทลูกค้าจับคู่จาก customer_code ก่อน ถ้าเว้นว่างจึงใช้ company_name — บริษัทต้องมีอยู่ในระบบแล้ว</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+          <t xml:space="preserve">ลำดับการจับคู่บริษัท: customer_code → tax_id → company_name — บริษัทต้องมีอยู่ในระบบแล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลูกค้าเดิมในระบบส่วนใหญ่ไม่มี customer_code แต่มี tax_id — ถ้าผูกกับลูกค้าเดิม แนะนำให้ใช้ tax_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">คอลัมน์</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ชื่อหัวคอลัมน์</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">จำเป็น</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ชนิดข้อมูล</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">คำอธิบาย</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ใช่</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ข้อความ</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ชื่อไซต์งาน เช่น “โรงงานบางปู เฟส 2” — ถ้าเว้นว่างแถวนั้นจะถูกข้าม</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">แนะนำ</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -510,24 +513,24 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">รหัสลูกค้า (ตรงกับ customer_code ในเทมเพลตลูกค้า) — วิธีจับคู่บริษัทที่แม่นที่สุด</t>
+          <t xml:space="preserve">ชื่อไซต์งาน เช่น “PT สันทราย เชียงใหม่” — ถ้าเว้นว่างแถวนั้นจะถูกข้าม</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">company_name</t>
+          <t xml:space="preserve">tax_id</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">แนะนำ</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -537,19 +540,19 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อบริษัทลูกค้า — ใช้จับคู่เมื่อไม่ได้ใส่ customer_code ต้องสะกดตรงกับที่มีในระบบ</t>
+          <t xml:space="preserve">เลขผู้เสียภาษีของบริษัทเจ้าของไซต์ — วิธีจับคู่ที่ครอบคลุมที่สุดสำหรับลูกค้าเดิม</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -564,19 +567,19 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ที่อยู่ไซต์งานแบบเต็ม (ใส่ในช่องเดียว ขึ้นบรรทัดใหม่ด้วย Alt+Enter ได้)</t>
+          <t xml:space="preserve">รหัสลูกค้าของบริษัทเจ้าของไซต์ — ถ้ากรอกจะใช้จับคู่ก่อน tax_id</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_url</t>
+          <t xml:space="preserve">company_name</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -586,24 +589,24 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลิงก์ Google Maps ของไซต์ ช่างจะกดเปิดนำทางจากหน้าใบงานได้เลย</t>
+          <t xml:space="preserve">ชื่อบริษัทลูกค้า — ใช้จับคู่เมื่อไม่ได้ใส่ทั้ง customer_code และ tax_id ต้องสะกดตรงกับที่มีในระบบเป๊ะๆ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">F</t>
+          <t xml:space="preserve">E</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact_name</t>
+          <t xml:space="preserve">address</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -618,19 +621,19 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อผู้ติดต่อประจำไซต์ (ชื่อ เว้นวรรค นามสกุล) ต้องเป็นผู้ติดต่อที่มีอยู่แล้วในระบบ</t>
+          <t xml:space="preserve">ที่อยู่ไซต์งานแบบเต็ม (ใส่ในช่องเดียว ขึ้นบรรทัดใหม่ด้วย Alt+Enter ได้) · ถ้ามีแต่พิกัด ใช้รูปแบบเดิมที่ใช้อยู่ได้เลย เช่น “พิกัด 18.871070, 98.980124”</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">F</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact_phone</t>
+          <t xml:space="preserve">map_url</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -640,37 +643,91 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ข้อความ</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">เบอร์ผู้ติดต่อ — ใช้ช่วยแยกกรณีชื่อซ้ำกัน ไม่ได้บันทึกลงไซต์โดยตรง</t>
+          <t xml:space="preserve">ลิงก์ Google Maps ของไซต์ ช่างจะกดเปิดนำทางจากหน้าใบงานได้เลย</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contact_name</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ข้อความ</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ชื่อผู้ติดต่อประจำไซต์ (ชื่อ เว้นวรรค นามสกุล) ต้องเป็นผู้ติดต่อที่มีอยู่แล้วในระบบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">H</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contact_phone</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ข้อความ</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เบอร์ผู้ติดต่อ — ใช้ช่วยแยกกรณีชื่อซ้ำกัน ไม่ได้บันทึกลงไซต์โดยตรง</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">หมายเหตุอื่นๆ เช่น เงื่อนไขการเข้าพื้นที่ เวลาเปิด-ปิด</t>
         </is>
